--- a/datasets/segundos_clientes/ventas.xlsx
+++ b/datasets/segundos_clientes/ventas.xlsx
@@ -1,43 +1,88 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="ventas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ventas" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="15">
+  <si>
+    <t>id_venta</t>
+  </si>
+  <si>
+    <t>id_cliente</t>
+  </si>
+  <si>
+    <t>producto</t>
+  </si>
+  <si>
+    <t>cantidad</t>
+  </si>
+  <si>
+    <t>importe</t>
+  </si>
+  <si>
+    <t>Monitor Samsung 24</t>
+  </si>
+  <si>
+    <t>Raton inalambrico</t>
+  </si>
+  <si>
+    <t>Impresora Canon</t>
+  </si>
+  <si>
+    <t>Mochila portatil</t>
+  </si>
+  <si>
+    <t>Tablet Lenovo 10</t>
+  </si>
+  <si>
+    <t>Portatil HP 15</t>
+  </si>
+  <si>
+    <t>SSD Kingston 480GB</t>
+  </si>
+  <si>
+    <t>Webcam Full HD</t>
+  </si>
+  <si>
+    <t>Auriculares JBL</t>
+  </si>
+  <si>
+    <t>Teclado mecanico</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,94 +90,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,101 +389,1728 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>cliente_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>producto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>cantidad</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>importe</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>10001</v>
+      </c>
+      <c r="B2">
+        <v>1041</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>259.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>10002</v>
+      </c>
+      <c r="B3">
+        <v>1020</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>10003</v>
+      </c>
+      <c r="B4">
+        <v>1094</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>10004</v>
+      </c>
+      <c r="B5">
+        <v>1021</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>124.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>10005</v>
+      </c>
+      <c r="B6">
+        <v>1078</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>59.96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>10006</v>
+      </c>
+      <c r="B7">
+        <v>1027</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>10007</v>
+      </c>
+      <c r="B8">
+        <v>1089</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>10008</v>
+      </c>
+      <c r="B9">
+        <v>1051</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>10009</v>
+      </c>
+      <c r="B10">
+        <v>1046</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>44.97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>10010</v>
+      </c>
+      <c r="B11">
+        <v>1091</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>197.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>10011</v>
+      </c>
+      <c r="B12">
+        <v>1072</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>10012</v>
+      </c>
+      <c r="B13">
+        <v>1015</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>10013</v>
+      </c>
+      <c r="B14">
+        <v>1011</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>649.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>10014</v>
+      </c>
+      <c r="B15">
+        <v>1069</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>59.96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>10015</v>
+      </c>
+      <c r="B16">
+        <v>1029</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>10016</v>
+      </c>
+      <c r="B17">
+        <v>1093</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>10017</v>
+      </c>
+      <c r="B18">
+        <v>1006</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>104.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>10018</v>
+      </c>
+      <c r="B19">
+        <v>1096</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>10019</v>
+      </c>
+      <c r="B20">
+        <v>1074</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>10020</v>
+      </c>
+      <c r="B21">
+        <v>1100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>119.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>10021</v>
+      </c>
+      <c r="B22">
+        <v>1044</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <v>159.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>10022</v>
+      </c>
+      <c r="B23">
+        <v>1023</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>129.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>10023</v>
+      </c>
+      <c r="B24">
+        <v>1031</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>136.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>10024</v>
+      </c>
+      <c r="B25">
+        <v>1057</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>74.84999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>10025</v>
+      </c>
+      <c r="B26">
+        <v>1062</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>227.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>10026</v>
+      </c>
+      <c r="B27">
+        <v>1079</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>649.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>10027</v>
+      </c>
+      <c r="B28">
+        <v>1035</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>74.84999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>10028</v>
+      </c>
+      <c r="B29">
+        <v>1040</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>10029</v>
+      </c>
+      <c r="B30">
+        <v>1080</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>10030</v>
+      </c>
+      <c r="B31">
+        <v>1098</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>10031</v>
+      </c>
+      <c r="B32">
+        <v>1032</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>10032</v>
+      </c>
+      <c r="B33">
+        <v>1013</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>10033</v>
+      </c>
+      <c r="B34">
+        <v>1082</v>
+      </c>
+      <c r="C34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>136.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>10034</v>
+      </c>
+      <c r="B35">
+        <v>1066</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>24.95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>10035</v>
+      </c>
+      <c r="B36">
+        <v>1012</v>
+      </c>
+      <c r="C36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>29.98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>10036</v>
+      </c>
+      <c r="B37">
+        <v>1010</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>10037</v>
+      </c>
+      <c r="B38">
+        <v>1055</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>10038</v>
+      </c>
+      <c r="B39">
+        <v>1005</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>10039</v>
+      </c>
+      <c r="B40">
+        <v>1039</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40">
+        <v>159.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>10040</v>
+      </c>
+      <c r="B41">
+        <v>1085</v>
+      </c>
+      <c r="C41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+      <c r="E41">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>10041</v>
+      </c>
+      <c r="B42">
+        <v>1019</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>10042</v>
+      </c>
+      <c r="B43">
+        <v>1081</v>
+      </c>
+      <c r="C43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>10043</v>
+      </c>
+      <c r="B44">
+        <v>1064</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>10044</v>
+      </c>
+      <c r="B45">
+        <v>1028</v>
+      </c>
+      <c r="C45" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45">
+        <v>5</v>
+      </c>
+      <c r="E45">
+        <v>74.95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>10045</v>
+      </c>
+      <c r="B46">
+        <v>1036</v>
+      </c>
+      <c r="C46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46">
+        <v>5</v>
+      </c>
+      <c r="E46">
+        <v>74.95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>10046</v>
+      </c>
+      <c r="B47">
+        <v>1092</v>
+      </c>
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47">
+        <v>5</v>
+      </c>
+      <c r="E47">
+        <v>74.95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>10047</v>
+      </c>
+      <c r="B48">
+        <v>1008</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>10048</v>
+      </c>
+      <c r="B49">
+        <v>1084</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>124.75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>10049</v>
+      </c>
+      <c r="B50">
+        <v>1090</v>
+      </c>
+      <c r="C50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>10050</v>
+      </c>
+      <c r="B51">
+        <v>1005</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>129.9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>10051</v>
+      </c>
+      <c r="B52">
+        <v>1056</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <v>519.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>10052</v>
+      </c>
+      <c r="B53">
+        <v>1022</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53">
+        <v>5</v>
+      </c>
+      <c r="E53">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54">
+        <v>10053</v>
+      </c>
+      <c r="B54">
+        <v>1076</v>
+      </c>
+      <c r="C54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55">
+        <v>10054</v>
+      </c>
+      <c r="B55">
+        <v>1067</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55">
+        <v>5</v>
+      </c>
+      <c r="E55">
+        <v>199.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56">
+        <v>10055</v>
+      </c>
+      <c r="B56">
+        <v>1002</v>
+      </c>
+      <c r="C56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>24.95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57">
+        <v>10056</v>
+      </c>
+      <c r="B57">
+        <v>1073</v>
+      </c>
+      <c r="C57" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58">
+        <v>10057</v>
+      </c>
+      <c r="B58">
+        <v>1017</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59">
+        <v>10058</v>
+      </c>
+      <c r="B59">
+        <v>1030</v>
+      </c>
+      <c r="C59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59">
+        <v>5</v>
+      </c>
+      <c r="E59">
+        <v>74.95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>10059</v>
+      </c>
+      <c r="B60">
+        <v>1052</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60">
+        <v>39.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61">
+        <v>10060</v>
+      </c>
+      <c r="B61">
+        <v>1063</v>
+      </c>
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>10061</v>
+      </c>
+      <c r="B62">
+        <v>1097</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63">
+        <v>10062</v>
+      </c>
+      <c r="B63">
+        <v>1070</v>
+      </c>
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>129.9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64">
+        <v>10063</v>
+      </c>
+      <c r="B64">
+        <v>1088</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64">
+        <v>119.7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>10064</v>
+      </c>
+      <c r="B65">
+        <v>1042</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>129.9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>10065</v>
+      </c>
+      <c r="B66">
+        <v>1026</v>
+      </c>
+      <c r="C66" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
+      <c r="E66">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67">
+        <v>10066</v>
+      </c>
+      <c r="B67">
+        <v>1049</v>
+      </c>
+      <c r="C67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67">
+        <v>5</v>
+      </c>
+      <c r="E67">
+        <v>174.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>10067</v>
+      </c>
+      <c r="B68">
+        <v>1038</v>
+      </c>
+      <c r="C68" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>10068</v>
+      </c>
+      <c r="B69">
+        <v>1034</v>
+      </c>
+      <c r="C69" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>10069</v>
+      </c>
+      <c r="B70">
+        <v>1066</v>
+      </c>
+      <c r="C70" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70">
+        <v>4</v>
+      </c>
+      <c r="E70">
+        <v>519.6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>10070</v>
+      </c>
+      <c r="B71">
+        <v>1054</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+      <c r="E71">
+        <v>199.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>10071</v>
+      </c>
+      <c r="B72">
+        <v>1045</v>
+      </c>
+      <c r="C72" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+      <c r="E72">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>10072</v>
+      </c>
+      <c r="B73">
+        <v>1099</v>
+      </c>
+      <c r="C73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+      <c r="E73">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74">
+        <v>10073</v>
+      </c>
+      <c r="B74">
+        <v>1003</v>
+      </c>
+      <c r="C74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74">
+        <v>5</v>
+      </c>
+      <c r="E74">
+        <v>197.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>10074</v>
+      </c>
+      <c r="B75">
+        <v>1016</v>
+      </c>
+      <c r="C75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+      <c r="E75">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>10075</v>
+      </c>
+      <c r="B76">
+        <v>1061</v>
+      </c>
+      <c r="C76" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>10076</v>
+      </c>
+      <c r="B77">
+        <v>1025</v>
+      </c>
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77">
+        <v>5</v>
+      </c>
+      <c r="E77">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78">
+        <v>10077</v>
+      </c>
+      <c r="B78">
+        <v>1047</v>
+      </c>
+      <c r="C78" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78">
+        <v>4</v>
+      </c>
+      <c r="E78">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>10078</v>
+      </c>
+      <c r="B79">
+        <v>1060</v>
+      </c>
+      <c r="C79" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79">
+        <v>4</v>
+      </c>
+      <c r="E79">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80">
+        <v>10079</v>
+      </c>
+      <c r="B80">
+        <v>1075</v>
+      </c>
+      <c r="C80" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>10080</v>
+      </c>
+      <c r="B81">
+        <v>1048</v>
+      </c>
+      <c r="C81" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81">
+        <v>5</v>
+      </c>
+      <c r="E81">
+        <v>124.75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82">
+        <v>10081</v>
+      </c>
+      <c r="B82">
+        <v>1050</v>
+      </c>
+      <c r="C82" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83">
+        <v>10082</v>
+      </c>
+      <c r="B83">
+        <v>1033</v>
+      </c>
+      <c r="C83" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83">
+        <v>3</v>
+      </c>
+      <c r="E83">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84">
+        <v>10083</v>
+      </c>
+      <c r="B84">
+        <v>1024</v>
+      </c>
+      <c r="C84" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85">
+        <v>10084</v>
+      </c>
+      <c r="B85">
+        <v>1044</v>
+      </c>
+      <c r="C85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85">
+        <v>2</v>
+      </c>
+      <c r="E85">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86">
+        <v>10085</v>
+      </c>
+      <c r="B86">
+        <v>1071</v>
+      </c>
+      <c r="C86" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87">
+        <v>10086</v>
+      </c>
+      <c r="B87">
+        <v>1095</v>
+      </c>
+      <c r="C87" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87">
+        <v>3</v>
+      </c>
+      <c r="E87">
+        <v>136.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88">
+        <v>10087</v>
+      </c>
+      <c r="B88">
+        <v>1077</v>
+      </c>
+      <c r="C88" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+      <c r="E88">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89">
+        <v>10088</v>
+      </c>
+      <c r="B89">
+        <v>1083</v>
+      </c>
+      <c r="C89" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90">
+        <v>10089</v>
+      </c>
+      <c r="B90">
+        <v>1087</v>
+      </c>
+      <c r="C90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+      <c r="E90">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91">
+        <v>10090</v>
+      </c>
+      <c r="B91">
+        <v>1037</v>
+      </c>
+      <c r="C91" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+      <c r="E91">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92">
+        <v>10091</v>
+      </c>
+      <c r="B92">
+        <v>1018</v>
+      </c>
+      <c r="C92" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92">
+        <v>4</v>
+      </c>
+      <c r="E92">
+        <v>59.96</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93">
+        <v>10092</v>
+      </c>
+      <c r="B93">
+        <v>1009</v>
+      </c>
+      <c r="C93" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94">
+        <v>10093</v>
+      </c>
+      <c r="B94">
+        <v>1086</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94">
+        <v>4</v>
+      </c>
+      <c r="E94">
+        <v>519.6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95">
+        <v>10094</v>
+      </c>
+      <c r="B95">
+        <v>1068</v>
+      </c>
+      <c r="C95" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>24.95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96">
+        <v>10095</v>
+      </c>
+      <c r="B96">
         <v>1001</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Hotel 3 noches</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>120.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1002</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Vuelo</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="C96" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96">
+        <v>4</v>
+      </c>
+      <c r="E96">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97">
+        <v>10096</v>
+      </c>
+      <c r="B97">
+        <v>1058</v>
+      </c>
+      <c r="C97" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1003</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Tour guiado</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1005</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Hotel 1 noche</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>80</v>
+      <c r="E97">
+        <v>29.98</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98">
+        <v>10097</v>
+      </c>
+      <c r="B98">
+        <v>1053</v>
+      </c>
+      <c r="C98" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98">
+        <v>4</v>
+      </c>
+      <c r="E98">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99">
+        <v>10098</v>
+      </c>
+      <c r="B99">
+        <v>1043</v>
+      </c>
+      <c r="C99" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99">
+        <v>4</v>
+      </c>
+      <c r="E99">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100">
+        <v>10099</v>
+      </c>
+      <c r="B100">
+        <v>1065</v>
+      </c>
+      <c r="C100" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100">
+        <v>3</v>
+      </c>
+      <c r="E100">
+        <v>119.7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101">
+        <v>10100</v>
+      </c>
+      <c r="B101">
+        <v>1059</v>
+      </c>
+      <c r="C101" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101">
+        <v>4</v>
+      </c>
+      <c r="E101">
+        <v>2396</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>